--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/VIRGINIA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/VIRGINIA_2022.xlsx
@@ -499,7 +499,7 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="9">
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="12">
@@ -715,7 +715,7 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="21">
@@ -733,7 +733,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="22">
@@ -1039,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="39">
@@ -1075,7 +1075,7 @@
         <v>3</v>
       </c>
       <c r="D40">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="41">
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="D55">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="56">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D57">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="58">
@@ -1417,7 +1417,7 @@
         <v>3</v>
       </c>
       <c r="D59">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="60">
@@ -1597,7 +1597,7 @@
         <v>3</v>
       </c>
       <c r="D69">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="70">
@@ -1687,7 +1687,7 @@
         <v>3</v>
       </c>
       <c r="D74">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="75">
@@ -1723,7 +1723,7 @@
         <v>3</v>
       </c>
       <c r="D76">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="77">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C88">
@@ -2101,7 +2101,7 @@
         <v>3</v>
       </c>
       <c r="D97">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="98">
@@ -2371,7 +2371,7 @@
         <v>3</v>
       </c>
       <c r="D112">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="113">
@@ -2407,7 +2407,7 @@
         <v>3</v>
       </c>
       <c r="D114">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="115">
@@ -2461,7 +2461,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="118">
@@ -2659,7 +2659,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="129">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="135">
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="D151">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="152">
@@ -3199,7 +3199,7 @@
         <v>3</v>
       </c>
       <c r="D158">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="159">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C177">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C185">
@@ -3703,7 +3703,7 @@
         <v>3</v>
       </c>
       <c r="D186">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="187">
@@ -3721,7 +3721,7 @@
         <v>3</v>
       </c>
       <c r="D187">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="188">
@@ -3955,7 +3955,7 @@
         <v>3</v>
       </c>
       <c r="D200">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="201">
@@ -4369,7 +4369,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="224">
@@ -4405,7 +4405,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="226">
@@ -4513,7 +4513,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="232">
@@ -4549,7 +4549,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="234">
@@ -4783,7 +4783,7 @@
         <v>3</v>
       </c>
       <c r="D246">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="247">
@@ -4909,7 +4909,7 @@
         <v>3</v>
       </c>
       <c r="D253">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="254">
@@ -5089,7 +5089,7 @@
         <v>3</v>
       </c>
       <c r="D263">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="264">
@@ -5161,7 +5161,7 @@
         <v>3</v>
       </c>
       <c r="D267">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="268">
@@ -5233,7 +5233,7 @@
         <v>3</v>
       </c>
       <c r="D271">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="272">
@@ -5323,7 +5323,7 @@
         <v>3</v>
       </c>
       <c r="D276">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="277">
@@ -5485,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="D285">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="286">
@@ -5593,7 +5593,7 @@
         <v>3</v>
       </c>
       <c r="D291">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="292">
@@ -5647,7 +5647,7 @@
         <v>3</v>
       </c>
       <c r="D294">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="295">
@@ -5737,7 +5737,7 @@
         <v>3</v>
       </c>
       <c r="D299">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="300">
@@ -5791,7 +5791,7 @@
         <v>3</v>
       </c>
       <c r="D302">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="303">
@@ -5953,7 +5953,7 @@
         <v>3</v>
       </c>
       <c r="D311">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="312">
@@ -6403,7 +6403,7 @@
         <v>3</v>
       </c>
       <c r="D336">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="337">
@@ -6493,7 +6493,7 @@
         <v>3</v>
       </c>
       <c r="D341">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="342">
@@ -6565,7 +6565,7 @@
         <v>3</v>
       </c>
       <c r="D345">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="346">
@@ -6943,7 +6943,7 @@
         <v>3</v>
       </c>
       <c r="D366">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="367">
@@ -7051,7 +7051,7 @@
         <v>3</v>
       </c>
       <c r="D372">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="373">
@@ -7231,7 +7231,7 @@
         <v>3</v>
       </c>
       <c r="D382">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="383">
@@ -7267,7 +7267,7 @@
         <v>3</v>
       </c>
       <c r="D384">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="385">
@@ -7285,7 +7285,7 @@
         <v>3</v>
       </c>
       <c r="D385">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="386">
@@ -7393,7 +7393,7 @@
         <v>3</v>
       </c>
       <c r="D391">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="392">
@@ -7645,7 +7645,7 @@
         <v>3</v>
       </c>
       <c r="D405">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="406">
@@ -7789,7 +7789,7 @@
         <v>3</v>
       </c>
       <c r="D413">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="414">
@@ -8257,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="D439">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="440">
@@ -8329,7 +8329,7 @@
         <v>3</v>
       </c>
       <c r="D443">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="444">
@@ -8466,14 +8466,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C451">
         <v>3</v>
       </c>
       <c r="D451">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="452">
@@ -8545,7 +8545,7 @@
         <v>3</v>
       </c>
       <c r="D455">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="456">
@@ -8563,7 +8563,7 @@
         <v>3</v>
       </c>
       <c r="D456">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="457">
@@ -8743,7 +8743,7 @@
         <v>3</v>
       </c>
       <c r="D466">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="467">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C470">
@@ -8959,7 +8959,7 @@
         <v>3</v>
       </c>
       <c r="D478">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="479">
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="D479">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="480">
@@ -9013,7 +9013,7 @@
         <v>3</v>
       </c>
       <c r="D481">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="482">
@@ -9049,7 +9049,7 @@
         <v>3</v>
       </c>
       <c r="D483">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="484">
@@ -9571,7 +9571,7 @@
         <v>3</v>
       </c>
       <c r="D512">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="513">
@@ -9661,7 +9661,7 @@
         <v>3</v>
       </c>
       <c r="D517">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="518">
@@ -9967,7 +9967,7 @@
         <v>3</v>
       </c>
       <c r="D534">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="535">
@@ -9985,7 +9985,7 @@
         <v>3</v>
       </c>
       <c r="D535">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="536">
@@ -10687,7 +10687,7 @@
         <v>3</v>
       </c>
       <c r="D574">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="575">
@@ -10723,7 +10723,7 @@
         <v>3</v>
       </c>
       <c r="D576">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="577">
@@ -10813,7 +10813,7 @@
         <v>3</v>
       </c>
       <c r="D581">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="582">
@@ -10867,7 +10867,7 @@
         <v>3</v>
       </c>
       <c r="D584">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="585">
@@ -10885,7 +10885,7 @@
         <v>3</v>
       </c>
       <c r="D585">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="586">
@@ -10975,7 +10975,7 @@
         <v>3</v>
       </c>
       <c r="D590">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="591">
@@ -11011,7 +11011,7 @@
         <v>3</v>
       </c>
       <c r="D592">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="593">
@@ -11209,7 +11209,7 @@
         <v>3</v>
       </c>
       <c r="D603">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="604">
@@ -11263,7 +11263,7 @@
         <v>3</v>
       </c>
       <c r="D606">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="607">
@@ -11299,7 +11299,7 @@
         <v>3</v>
       </c>
       <c r="D608">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="609">
@@ -11515,7 +11515,7 @@
         <v>3</v>
       </c>
       <c r="D620">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="621">
@@ -11623,7 +11623,7 @@
         <v>3</v>
       </c>
       <c r="D626">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="627">
@@ -11641,7 +11641,7 @@
         <v>3</v>
       </c>
       <c r="D627">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="628">
@@ -11713,7 +11713,7 @@
         <v>3</v>
       </c>
       <c r="D631">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="632">
@@ -11803,7 +11803,7 @@
         <v>3</v>
       </c>
       <c r="D636">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="637">
@@ -11875,7 +11875,7 @@
         <v>3</v>
       </c>
       <c r="D640">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="641">
@@ -11983,7 +11983,7 @@
         <v>3</v>
       </c>
       <c r="D646">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="647">
@@ -12307,7 +12307,7 @@
         <v>3</v>
       </c>
       <c r="D664">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="665">
@@ -12325,7 +12325,7 @@
         <v>3</v>
       </c>
       <c r="D665">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="666">
@@ -12361,7 +12361,7 @@
         <v>3</v>
       </c>
       <c r="D667">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="668">
@@ -12451,7 +12451,7 @@
         <v>3</v>
       </c>
       <c r="D672">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="673">
@@ -12595,7 +12595,7 @@
         <v>3</v>
       </c>
       <c r="D680">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="681">
@@ -12847,7 +12847,7 @@
         <v>3</v>
       </c>
       <c r="D694">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="695">
@@ -13135,7 +13135,7 @@
         <v>3</v>
       </c>
       <c r="D710">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="711">
@@ -13747,7 +13747,7 @@
         <v>3</v>
       </c>
       <c r="D744">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="745">
@@ -13819,7 +13819,7 @@
         <v>3</v>
       </c>
       <c r="D748">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="749">
@@ -13945,7 +13945,7 @@
         <v>3</v>
       </c>
       <c r="D755">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="756">
@@ -14035,7 +14035,7 @@
         <v>3</v>
       </c>
       <c r="D760">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="761">
@@ -14233,7 +14233,7 @@
         <v>3</v>
       </c>
       <c r="D771">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="772">
@@ -14449,7 +14449,7 @@
         <v>3</v>
       </c>
       <c r="D783">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="784">
@@ -14557,7 +14557,7 @@
         <v>3</v>
       </c>
       <c r="D789">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="790">
@@ -14593,7 +14593,7 @@
         <v>3</v>
       </c>
       <c r="D791">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="792">
@@ -14701,7 +14701,7 @@
         <v>3</v>
       </c>
       <c r="D797">
-        <v>0.0009143553794574825</v>
+        <v>0.0009143553794574824</v>
       </c>
     </row>
     <row r="798">
